--- a/Configs/GameConfig/Datas/cell/#AbilityEffect-技能效果.xlsx
+++ b/Configs/GameConfig/Datas/cell/#AbilityEffect-技能效果.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3398,6 +3398,290 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C40" t="n">
+        <v>29</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Spawn</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>13</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>2901</v>
+      </c>
+      <c r="C41" t="n">
+        <v>29</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Spawn</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>12</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>14</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>2902</v>
+      </c>
+      <c r="C42" t="n">
+        <v>29</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Spawn</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>15</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>2903</v>
+      </c>
+      <c r="C43" t="n">
+        <v>29</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Slowed</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
